--- a/server/data/users.xlsx
+++ b/server/data/users.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kenoxia/Documents/UGit/lottery/server/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24DD8D7-003A-784B-9AE4-98FE4AF7ACA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987F67DC-1A0D-544C-99F9-EF0F3A21C1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>工号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,275 +39,248 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>夏超男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雪姐姐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>弟弟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郗雪洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王世洲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>郑庆哲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方任哲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>陈女士</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>芭乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000026</t>
+  </si>
+  <si>
+    <t>000027</t>
+  </si>
+  <si>
+    <t>000028</t>
+  </si>
+  <si>
+    <t>000029</t>
+  </si>
+  <si>
+    <t>000030</t>
+  </si>
+  <si>
+    <t>000031</t>
+  </si>
+  <si>
+    <t>000032</t>
+  </si>
+  <si>
+    <t>000033</t>
+  </si>
+  <si>
+    <t>000034</t>
+  </si>
+  <si>
+    <t>000035</t>
+  </si>
+  <si>
+    <t>000036</t>
+  </si>
+  <si>
+    <t>煤球</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>招行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>建行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拖把</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李思</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小男男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>王师傅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>胖胖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李婷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李先生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豪哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>悦悦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>君哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vampire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>keno</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shizhou</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chanze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李狗蛋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李狗嗨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>李妍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>老爷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大哥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>谭奕彬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>000002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000005</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000009</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000010</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000011</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000014</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000015</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000016</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000017</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>000018</t>
   </si>
   <si>
     <t>000019</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000020</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000021</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000023</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000024</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>000025</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏超男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>雪姐姐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>弟弟</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郗雪洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王世洲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>郑庆哲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>方任哲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>陈女士</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>芭乐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>000026</t>
-  </si>
-  <si>
-    <t>000027</t>
-  </si>
-  <si>
-    <t>000028</t>
-  </si>
-  <si>
-    <t>000029</t>
-  </si>
-  <si>
-    <t>000030</t>
-  </si>
-  <si>
-    <t>000031</t>
-  </si>
-  <si>
-    <t>000032</t>
-  </si>
-  <si>
-    <t>000033</t>
-  </si>
-  <si>
-    <t>000034</t>
-  </si>
-  <si>
-    <t>000035</t>
-  </si>
-  <si>
-    <t>000036</t>
-  </si>
-  <si>
-    <t>000037</t>
-  </si>
-  <si>
-    <t>煤球</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>招行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>建行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小金</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拖把</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李思</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小男男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>王师傅</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>胖胖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李婷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李先生</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>豪哥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>悦悦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>君哥</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>vampire</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>keno</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>shizhou</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>chanze</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吴赫</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李狗蛋</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李狗嗨</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李妍</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>diga</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>李狗down</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>老爷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大哥</t>
+  </si>
+  <si>
+    <t>迪迦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小小</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -353,12 +326,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -390,7 +369,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -404,6 +383,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -735,291 +720,291 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="19">
-      <c r="A2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>28</v>
+      <c r="A2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="19">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="19">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="19">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="19">
       <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>55</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="19">
       <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:2" ht="19">
-      <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
+      <c r="A8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="19">
       <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="19">
       <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="19">
       <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="19">
       <c r="A12" s="2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="19">
-      <c r="A13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>47</v>
+      <c r="A13" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="19">
       <c r="A14" s="2" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="19">
       <c r="A15" s="2" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="19">
       <c r="A16" s="2" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="19">
       <c r="A17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="19">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>59</v>
+      <c r="A18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="19">
       <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="19">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="19">
       <c r="A21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>26</v>
+        <v>67</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="19">
       <c r="A22" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>30</v>
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="19">
-      <c r="A23" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>31</v>
+      <c r="A23" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="19">
       <c r="A24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="19">
       <c r="A25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="19">
       <c r="A26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="19">
       <c r="A27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>63</v>
+        <v>13</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="19">
-      <c r="A28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>64</v>
+      <c r="A28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="19">
       <c r="A29" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>67</v>
+        <v>14</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="19">
       <c r="A30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>68</v>
+        <v>15</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="19">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>69</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="19">
       <c r="A32" s="2" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="19">
       <c r="A33" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="19">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="19">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="19">
       <c r="A36" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="19">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>66</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2">
